--- a/output/pdf_financials_xlsx/MUX.xlsx
+++ b/output/pdf_financials_xlsx/MUX.xlsx
@@ -1030,16 +1030,16 @@
         <v>-8.645</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1.091</v>
+        <v>-1.091</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>-12.249</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>35.754</v>
+        <v>-35.754</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>97.59699999999999</v>
+        <v>-97.59699999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1234,16 +1234,16 @@
         <v>-8.645</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.091</v>
+        <v>-1.091</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-12.249</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>35.754</v>
+        <v>-35.754</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>97.59699999999999</v>
+        <v>-97.59699999999999</v>
       </c>
     </row>
     <row r="21">
@@ -1354,16 +1354,16 @@
         <v>-8.645</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1.091</v>
+        <v>-1.091</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>-12.249</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>35.754</v>
+        <v>-35.754</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>97.59699999999999</v>
+        <v>-97.59699999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1562,16 +1562,16 @@
         <v>-10.642</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.186</v>
+        <v>-2.368</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-15.509</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>26.825</v>
+        <v>-44.683</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>91.483</v>
+        <v>-103.711</v>
       </c>
     </row>
     <row r="28">
@@ -1642,16 +1642,16 @@
         <v>-9.816000000000001</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.517</v>
+        <v>-1.665</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-14.939</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>27.336</v>
+        <v>-44.172</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>91.955</v>
+        <v>-103.239</v>
       </c>
     </row>
     <row r="30">
@@ -1682,16 +1682,16 @@
         <v>-3.790385796092999</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.212347362497895</v>
+        <v>-0.6838652970193331</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>-6.16140327722809</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>9.31903796001159</v>
+        <v>-15.05855080368862</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>21.06537585734511</v>
+        <v>-23.65035439221849</v>
       </c>
     </row>
     <row r="31">
@@ -1722,16 +1722,16 @@
         <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1762,16 +1762,16 @@
         <v>-3.33821161442787</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.448106329758614</v>
+        <v>-0.448106329758614</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>-5.051946498612148</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>12.1887943818501</v>
+        <v>-12.1887943818501</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>22.3578651247818</v>
+        <v>-22.3578651247818</v>
       </c>
     </row>
     <row r="33">
@@ -4664,16 +4664,16 @@
         <v>-8.645</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>1.091</v>
+        <v>-1.091</v>
       </c>
       <c r="J99" s="3" t="n">
         <v>-12.249</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>35.754</v>
+        <v>-35.754</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>97.59699999999999</v>
+        <v>-97.59699999999999</v>
       </c>
     </row>
     <row r="100">
@@ -21126,10 +21126,10 @@
         <v>-12.249</v>
       </c>
       <c r="N218" s="5" t="n">
-        <v>35.754</v>
+        <v>-35.754</v>
       </c>
       <c r="O218" s="5" t="n">
-        <v>97.59699999999999</v>
+        <v>-97.59699999999999</v>
       </c>
     </row>
     <row r="219">
@@ -23012,13 +23012,13 @@
         </is>
       </c>
       <c r="L246" s="5" t="n">
-        <v>1.091</v>
+        <v>-1.091</v>
       </c>
       <c r="M246" s="5" t="n">
         <v>-12.249</v>
       </c>
       <c r="N246" s="5" t="n">
-        <v>35.754</v>
+        <v>-35.754</v>
       </c>
       <c r="O246" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
         <v>-8.645</v>
       </c>
       <c r="L265" s="5" t="n">
-        <v>1.091</v>
+        <v>-1.091</v>
       </c>
       <c r="M265" s="5" t="n">
         <v>-12.249</v>

--- a/output/pdf_financials_xlsx/MUX.xlsx
+++ b/output/pdf_financials_xlsx/MUX.xlsx
@@ -21670,7 +21670,11 @@
           <t>Interest expense2</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MUX.xlsx
+++ b/output/pdf_financials_xlsx/MUX.xlsx
@@ -1584,10 +1584,10 @@
         <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>46.817</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>45.192</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>6.576</v>
@@ -1599,19 +1599,19 @@
         <v>25.543</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.826</v>
+        <v>51.667</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.703</v>
+        <v>50.725</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.57</v>
+        <v>52.657</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.511</v>
+        <v>48.762</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.472</v>
+        <v>53.389</v>
       </c>
     </row>
     <row r="29">
@@ -1624,10 +1624,10 @@
         <v>-27.342</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-15.23</v>
+        <v>31.587</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-23.447</v>
+        <v>21.745</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-4.058</v>
@@ -1639,19 +1639,19 @@
         <v>-34.204</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-9.816000000000001</v>
+        <v>41.025</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.665</v>
+        <v>48.357</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-14.939</v>
+        <v>37.148</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-44.172</v>
+        <v>4.079</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-103.239</v>
+        <v>-50.322</v>
       </c>
     </row>
     <row r="30">
@@ -1664,10 +1664,10 @@
         <v>-11.3583303561785</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-7.149798369113622</v>
+        <v>14.82867242844334</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-12.59934335319753</v>
+        <v>11.68476654647845</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>-20.20916334661355</v>
@@ -1679,19 +1679,19 @@
         <v>-380.6365457378144</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-3.790385796092999</v>
+        <v>15.84154210316985</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-0.6838652970193331</v>
+        <v>19.86166616694528</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-6.16140327722809</v>
+        <v>15.32122691896841</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-15.05855080368862</v>
+        <v>1.390560280907495</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-23.65035439221849</v>
+        <v>-11.52794131796336</v>
       </c>
     </row>
     <row r="31">
@@ -4686,10 +4686,10 @@
         <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>46.817</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>45.192</v>
       </c>
       <c r="E100" s="3" t="n">
         <v>6.576</v>
@@ -4701,19 +4701,19 @@
         <v>25.543</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>51.667</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>50.725</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>52.657</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>48.762</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>53.389</v>
       </c>
     </row>
     <row r="101">
@@ -5172,10 +5172,10 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -12005,7 +12005,11 @@
           <t>Depreciation of property, plant and equipment 11</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -12066,7 +12070,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -16406,7 +16410,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MUX.xlsx
+++ b/output/pdf_financials_xlsx/MUX.xlsx
@@ -5292,13 +5292,13 @@
         <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>2.155</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>2.895</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>6.769</v>
       </c>
       <c r="H115" s="3" t="n">
         <v>0</v>
@@ -5864,10 +5864,8 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>18.922</v>
       </c>
       <c r="C129" s="3" t="n">
         <v>-30.792</v>
@@ -5884,30 +5882,20 @@
       <c r="G129" s="3" t="n">
         <v>70.00700000000001</v>
       </c>
-      <c r="H129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H129" s="3" t="n">
+        <v>-33.446</v>
+      </c>
+      <c r="I129" s="3" t="n">
+        <v>12.844</v>
+      </c>
+      <c r="J129" s="3" t="n">
+        <v>-23.677</v>
+      </c>
+      <c r="K129" s="3" t="n">
+        <v>-12.387</v>
+      </c>
+      <c r="L129" s="3" t="n">
+        <v>-5.813</v>
       </c>
     </row>
     <row r="130">
@@ -6116,10 +6104,8 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>46.672</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>67.54300000000001</v>
@@ -6136,30 +6122,20 @@
       <c r="G135" s="3" t="n">
         <v>-39.527</v>
       </c>
-      <c r="H135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H135" s="3" t="n">
+        <v>65.15900000000001</v>
+      </c>
+      <c r="I135" s="3" t="n">
+        <v>29.52</v>
+      </c>
+      <c r="J135" s="3" t="n">
+        <v>78.94199999999999</v>
+      </c>
+      <c r="K135" s="3" t="n">
+        <v>84.986</v>
+      </c>
+      <c r="L135" s="3" t="n">
+        <v>154.147</v>
       </c>
     </row>
   </sheetData>
@@ -12807,7 +12783,11 @@
           <t>Net cash flows generated from operating activities</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E98" s="5" t="n">
         <v>46.672</v>
       </c>
@@ -16554,7 +16534,11 @@
           <t>Proceeds from sale of investments (note 5)</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
